--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484563_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484563_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5293</v>
+        <v>2.9689</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1271</v>
+        <v>3.5668</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5978</v>
@@ -610,10 +610,10 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.356</v>
+        <v>-0.9163</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1561</v>
+        <v>-0.7164</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1471</v>
+        <v>2.0535</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7256</v>
+        <v>2.7806</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5785</v>
+        <v>-0.7271</v>
       </c>
       <c r="G3" t="n">
         <v>0.7823</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5427</v>
+        <v>0.4491</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0565</v>
+        <v>-0.0015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5992</v>
+        <v>0.4506</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1462</v>
+        <v>1.3721</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6182</v>
+        <v>1.5221</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.472</v>
+        <v>-0.15</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6086</v>
@@ -766,13 +766,13 @@
         <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2996</v>
+        <v>-0.0737</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7127</v>
+        <v>0.6165</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0123</v>
+        <v>-0.6902</v>
       </c>
       <c r="V4" t="n">
         <v>1.1382</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1986</v>
+        <v>-0.0529</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0468</v>
+        <v>0.0494</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1519</v>
+        <v>-0.1023</v>
       </c>
       <c r="G7" t="n">
         <v>0.2709</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4617</v>
+        <v>-0.316</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1101</v>
+        <v>-0.0139</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3516</v>
+        <v>-0.302</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1911</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8908</v>
+        <v>-0.2064</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1404</v>
+        <v>0.6762</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0312</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-0.856</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8541</v>
+        <v>-0.1697</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.2349</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0834</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.4528</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2938</v>
+        <v>-0.6282</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.1802</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7701</v>
+        <v>-0.448</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4362</v>
@@ -1156,13 +1156,13 @@
         <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6842</v>
+        <v>-0.0187</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2353</v>
+        <v>0.5788</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9196</v>
+        <v>-0.5975</v>
       </c>
       <c r="V9" t="n">
         <v>0.8267</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4645</v>
+        <v>-1.6989</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5488</v>
+        <v>-1.7139</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0843</v>
+        <v>0.015</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6874</v>
+        <v>-1.0787</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9018</v>
+        <v>-0.8255</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7856</v>
+        <v>-0.2532</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7977</v>
+        <v>-0.4435</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1983</v>
+        <v>-0.511</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5994</v>
+        <v>0.0674</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8898</v>
+        <v>-0.6351</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7035</v>
+        <v>-0.3145</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1863</v>
+        <v>-0.3207</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5628</v>
+        <v>-0.2983</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7308</v>
+        <v>-0.3541</v>
       </c>
       <c r="U10" t="n">
-        <v>0.832</v>
+        <v>0.0558</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5764</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3095</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0865</v>
+        <v>-1.7726</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0024</v>
+        <v>-1.5348</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.2377</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0787</v>
+        <v>-3.6874</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8255</v>
+        <v>-1.9018</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2532</v>
+        <v>-1.7856</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4435</v>
+        <v>-0.7977</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.511</v>
+        <v>-0.1983</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0674</v>
+        <v>-0.5994</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6351</v>
+        <v>-2.8898</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3145</v>
+        <v>-1.7035</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3207</v>
+        <v>-1.1863</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6858</v>
+        <v>1.2547</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6425</v>
+        <v>0.7447</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0433</v>
+        <v>0.51</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>1.5764</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0.3095</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.059</v>
+        <v>-3.3391</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0965</v>
+        <v>-1.4261</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9625</v>
+        <v>-1.913</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1676</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0039</v>
+        <v>-0.2839</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2738</v>
+        <v>-0.0558</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2777</v>
+        <v>-0.2281</v>
       </c>
       <c r="V12" t="n">
         <v>0.945</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6177</v>
+        <v>-4.3164</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.935</v>
+        <v>-3.0674</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6827</v>
+        <v>-1.2489</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.796</v>
+        <v>-5.293</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9595</v>
+        <v>-3.1262</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1635</v>
+        <v>-2.1668</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1929</v>
+        <v>-2.675</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2604</v>
+        <v>-0.861</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0674</v>
+        <v>-1.814</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.603</v>
+        <v>-2.618</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-2.2652</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0961</v>
+        <v>-0.3528</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2317</v>
+        <v>-0.2898</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0068</v>
+        <v>-0.1304</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2249</v>
+        <v>-0.1593</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0376</v>
+        <v>0.7166</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6543</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0376</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.2645</v>
+        <v>-5.533</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8917</v>
+        <v>-3.553</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3728</v>
+        <v>-1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.293</v>
+        <v>-1.796</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.1262</v>
+        <v>-1.9595</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1668</v>
+        <v>0.1635</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.675</v>
+        <v>-1.1929</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.861</v>
+        <v>-1.2604</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.814</v>
+        <v>0.0674</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.618</v>
+        <v>-0.603</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2652</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3528</v>
+        <v>0.0961</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5498</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2379</v>
+        <v>0.3164</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9547</v>
+        <v>0.3888</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2832</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7166</v>
+        <v>-2.0376</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6543</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0623</v>
+        <v>-2.0376</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.1898</v>
+        <v>-10.5393</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.2871</v>
+        <v>-6.2897</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9027</v>
+        <v>-4.2496</v>
       </c>
       <c r="G15" t="n">
         <v>-6.7245</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9671</v>
+        <v>0.6177</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7195</v>
+        <v>0.7168</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2476</v>
+        <v>-0.0992</v>
       </c>
       <c r="V15" t="n">
         <v>-2.7832</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.9924</v>
+        <v>-20.4421</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.470499999999999</v>
+        <v>-7.919799999999999</v>
       </c>
       <c r="F16" t="n">
         <v>-12.522</v>
@@ -1672,7 +1672,7 @@
         <v>-17.4918</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1606000000000002</v>
+        <v>0.1606000000000006</v>
       </c>
       <c r="J16" t="n">
         <v>-1.8968</v>
@@ -1681,7 +1681,7 @@
         <v>-3.021</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1243</v>
+        <v>1.124299999999999</v>
       </c>
       <c r="M16" t="n">
         <v>-15.4346</v>
@@ -1702,16 +1702,16 @@
         <v>13.7444</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2788999999999995</v>
+        <v>0.2714999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9883000000000001</v>
+        <v>1.5386</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2673</v>
+        <v>-1.267</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6334999999999997</v>
+        <v>-0.6335000000000002</v>
       </c>
       <c r="W16" t="n">
         <v>8.931299999999998</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.3381</v>
+        <v>7.1225</v>
       </c>
       <c r="E17" t="n">
-        <v>5.3385</v>
+        <v>4.5693</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9995</v>
+        <v>2.5532</v>
       </c>
       <c r="G17" t="n">
         <v>6.416</v>
@@ -1780,13 +1780,13 @@
         <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3332</v>
+        <v>1.1176</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6833</v>
+        <v>0.914</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3501</v>
+        <v>0.2036</v>
       </c>
       <c r="V17" t="n">
         <v>0.3219</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.0771</v>
+        <v>6.364</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9763</v>
+        <v>4.4571</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1008</v>
+        <v>1.9069</v>
       </c>
       <c r="G18" t="n">
         <v>3.1487</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4286</v>
+        <v>0.7155</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2398</v>
+        <v>0.241</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6684</v>
+        <v>0.4745</v>
       </c>
       <c r="V18" t="n">
         <v>2.8663</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.4051</v>
+        <v>4.9374</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3754</v>
+        <v>1.8946</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0297</v>
+        <v>3.0428</v>
       </c>
       <c r="G19" t="n">
         <v>3.8494</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3774</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5664</v>
+        <v>0.0856</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.189</v>
+        <v>-0.1759</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6543</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3981</v>
+        <v>2.9955</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5823</v>
+        <v>1.7746</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8158</v>
+        <v>1.2209</v>
       </c>
       <c r="G20" t="n">
         <v>3.4062</v>
@@ -2014,13 +2014,13 @@
         <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.33</v>
+        <v>-0.7327</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5505</v>
+        <v>-0.3582</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7795</v>
+        <v>-0.3744</v>
       </c>
       <c r="V20" t="n">
         <v>0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0549</v>
+        <v>1.9689</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6127</v>
+        <v>1.3243</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4421</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>2.6728</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3901</v>
+        <v>-0.4761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0196</v>
+        <v>-0.3081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3705</v>
+        <v>-0.168</v>
       </c>
       <c r="V21" t="n">
         <v>0.3219</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.7561</v>
+        <v>1.8419</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1562</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5999</v>
+        <v>1.1237</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6022</v>
+        <v>1.6185</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.073</v>
+        <v>2.6314</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5292</v>
+        <v>-1.0129</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3182</v>
+        <v>2.2857</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3598</v>
+        <v>2.8177</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>-0.5319</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.284</v>
+        <v>-0.6673</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2869</v>
+        <v>-0.1863</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5709</v>
+        <v>-0.481</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8739</v>
+        <v>-0.0277</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2074</v>
+        <v>-0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6665</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5681</v>
+        <v>1.9005</v>
       </c>
       <c r="W22" t="n">
-        <v>1.267</v>
+        <v>2.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3011</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.01</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2374</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7725</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6185</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6314</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0129</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.2857</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8177</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5319</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1863</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.481</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8596</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6056</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2541</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.1971</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.9062</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9752999999999999</v>
+        <v>-3.6022</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9752999999999999</v>
+        <v>-2.073</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-1.5292</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9752999999999999</v>
+        <v>-2.3182</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9752999999999999</v>
+        <v>-2.3598</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-1.284</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.2869</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>-1.5709</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.3149</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.9728</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.5681</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5778</v>
+        <v>-0.0299</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2363</v>
+        <v>-0.044</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3414</v>
+        <v>0.0141</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7433999999999999</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.667</v>
+        <v>-0.1192</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1297</v>
+        <v>0.0626</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5373</v>
+        <v>-0.1818</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.8051</v>
+        <v>-1.1902</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.6424</v>
+        <v>-3.354</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8374</v>
+        <v>2.1638</v>
       </c>
       <c r="G27" t="n">
         <v>-1.3066</v>
@@ -2560,13 +2560,13 @@
         <v>1.0995</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6922</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2949</v>
+        <v>-0.0064</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3973</v>
+        <v>-0.0709</v>
       </c>
       <c r="V27" t="n">
         <v>0.0104</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.4626</v>
+        <v>-1.7982</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5129</v>
+        <v>-0.2244</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.9497</v>
+        <v>-1.5738</v>
       </c>
       <c r="G28" t="n">
         <v>-0.3397</v>
@@ -2638,13 +2638,13 @@
         <v>0.9163</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.1833</v>
+        <v>0.4811</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1456</v>
+        <v>0.434</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3288</v>
+        <v>0.0471</v>
       </c>
       <c r="V28" t="n">
         <v>-2.8559</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.7521</v>
+        <v>-2.044</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9159</v>
+        <v>-0.4351</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8362</v>
+        <v>-1.6089</v>
       </c>
       <c r="G29" t="n">
         <v>-0.3393</v>
@@ -2716,13 +2716,13 @@
         <v>1.6493</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6119</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.4955</v>
+        <v>-0.0147</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1164</v>
+        <v>0.1108</v>
       </c>
       <c r="V29" t="n">
         <v>-2.5339</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>20.9924</v>
+        <v>22.91559999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>12.5219</v>
+        <v>12.522</v>
       </c>
       <c r="F30" t="n">
-        <v>8.470400000000001</v>
+        <v>10.3936</v>
       </c>
       <c r="G30" t="n">
         <v>17.331</v>
@@ -2794,13 +2794,13 @@
         <v>16.4931</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2789999999999998</v>
+        <v>2.202</v>
       </c>
       <c r="T30" t="n">
-        <v>1.2671</v>
+        <v>1.267</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.9880999999999998</v>
+        <v>0.9349</v>
       </c>
       <c r="V30" t="n">
         <v>0.6334</v>
